--- a/servers/maze_main_server/conf.d/data/maze_equ_drop_v8【迷宫-装备掉落概率】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_equ_drop_v8【迷宫-装备掉落概率】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{304A3098-FBD4-4EC9-9B21-4B7B5AD0D501}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95505669-BBBF-46E9-9D12-6767AB1C35BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="24">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -76,8 +76,46 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>1,8,3,3,1,5</t>
+  </si>
+  <si>
+    <t>1:8000_3:2000_5:0_6:0</t>
+  </si>
+  <si>
+    <t>1,7,3,2,1,4</t>
+  </si>
+  <si>
+    <t>1:7000_3:3000_5:0_6:0</t>
+  </si>
+  <si>
+    <t>3,1,1,6,3,8</t>
+  </si>
+  <si>
+    <t>1:6000_3:4000_5:0_6:0</t>
+  </si>
+  <si>
+    <t>1:5000_3:4500_5:500_6:0</t>
+  </si>
+  <si>
+    <t>1:4000_3:5000_5:1000_6:0</t>
+  </si>
+  <si>
+    <t>1:3000_3:5500_5:1500_6:0</t>
+  </si>
+  <si>
+    <t>1:1800_3:6000_5:2000_6:200</t>
+  </si>
+  <si>
+    <t>1:1600_3:6000_5:2200_6:200</t>
+  </si>
+  <si>
+    <t>1:1400_3:6000_5:2400_6:200</t>
+  </si>
+  <si>
+    <t>1:1200_3:6000_5:2600_6:200</t>
+  </si>
+  <si>
     <t>0:0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -127,10 +165,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -463,1760 +506,1760 @@
       <c r="A5" s="1">
         <v>1</v>
       </c>
-      <c r="B5" s="1">
-        <v>0</v>
-      </c>
-      <c r="C5" s="2" t="s">
+      <c r="B5" s="2" t="s">
         <v>10</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>2</v>
       </c>
-      <c r="B6" s="1">
-        <v>0</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>10</v>
+      <c r="B6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>3</v>
       </c>
-      <c r="B7" s="1">
-        <v>0</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>10</v>
+      <c r="B7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>4</v>
       </c>
-      <c r="B8" s="1">
-        <v>0</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>10</v>
+      <c r="B8" s="2">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>5</v>
       </c>
-      <c r="B9" s="1">
-        <v>0</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>10</v>
+      <c r="B9" s="2">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>6</v>
       </c>
-      <c r="B10" s="1">
-        <v>0</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>10</v>
+      <c r="B10" s="2">
+        <v>0</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>7</v>
       </c>
-      <c r="B11" s="1">
-        <v>0</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>10</v>
+      <c r="B11" s="2">
+        <v>0</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>8</v>
       </c>
-      <c r="B12" s="1">
-        <v>0</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>10</v>
+      <c r="B12" s="2">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>9</v>
       </c>
-      <c r="B13" s="1">
-        <v>0</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>10</v>
+      <c r="B13" s="2">
+        <v>0</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>10</v>
       </c>
-      <c r="B14" s="1">
-        <v>0</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>10</v>
+      <c r="B14" s="2">
+        <v>0</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>11</v>
       </c>
-      <c r="B15" s="1">
-        <v>0</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>10</v>
+      <c r="B15" s="2">
+        <v>0</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>12</v>
       </c>
-      <c r="B16" s="1">
-        <v>0</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>10</v>
+      <c r="B16" s="2">
+        <v>0</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>13</v>
       </c>
-      <c r="B17" s="1">
-        <v>0</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>10</v>
+      <c r="B17" s="2">
+        <v>0</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <v>14</v>
       </c>
-      <c r="B18" s="1">
-        <v>0</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>10</v>
+      <c r="B18" s="2">
+        <v>0</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>15</v>
       </c>
-      <c r="B19" s="1">
-        <v>0</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>10</v>
+      <c r="B19" s="2">
+        <v>0</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <v>16</v>
       </c>
-      <c r="B20" s="1">
-        <v>0</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>10</v>
+      <c r="B20" s="2">
+        <v>0</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <v>17</v>
       </c>
-      <c r="B21" s="1">
-        <v>0</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>10</v>
+      <c r="B21" s="2">
+        <v>0</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <v>18</v>
       </c>
-      <c r="B22" s="1">
-        <v>0</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>10</v>
+      <c r="B22" s="2">
+        <v>0</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <v>19</v>
       </c>
-      <c r="B23" s="1">
-        <v>0</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>10</v>
+      <c r="B23" s="2">
+        <v>0</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <v>20</v>
       </c>
-      <c r="B24" s="1">
-        <v>0</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>10</v>
+      <c r="B24" s="2">
+        <v>0</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <v>21</v>
       </c>
-      <c r="B25" s="1">
-        <v>0</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>10</v>
+      <c r="B25" s="2">
+        <v>0</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <v>22</v>
       </c>
-      <c r="B26" s="1">
-        <v>0</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>10</v>
+      <c r="B26" s="2">
+        <v>0</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
         <v>23</v>
       </c>
-      <c r="B27" s="1">
-        <v>0</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>10</v>
+      <c r="B27" s="2">
+        <v>0</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
         <v>24</v>
       </c>
-      <c r="B28" s="1">
-        <v>0</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>10</v>
+      <c r="B28" s="2">
+        <v>0</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
         <v>25</v>
       </c>
-      <c r="B29" s="1">
-        <v>0</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>10</v>
+      <c r="B29" s="2">
+        <v>0</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
         <v>26</v>
       </c>
-      <c r="B30" s="1">
-        <v>0</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>10</v>
+      <c r="B30" s="2">
+        <v>0</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
         <v>27</v>
       </c>
-      <c r="B31" s="1">
-        <v>0</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>10</v>
+      <c r="B31" s="2">
+        <v>0</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32" s="1">
         <v>28</v>
       </c>
-      <c r="B32" s="1">
-        <v>0</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>10</v>
+      <c r="B32" s="2">
+        <v>0</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" s="1">
         <v>29</v>
       </c>
-      <c r="B33" s="1">
-        <v>0</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>10</v>
+      <c r="B33" s="2">
+        <v>0</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" s="1">
         <v>30</v>
       </c>
-      <c r="B34" s="1">
-        <v>0</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>10</v>
+      <c r="B34" s="2">
+        <v>0</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="1">
         <v>31</v>
       </c>
-      <c r="B35" s="1">
-        <v>0</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>10</v>
+      <c r="B35" s="2">
+        <v>0</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" s="1">
         <v>32</v>
       </c>
-      <c r="B36" s="1">
-        <v>0</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>10</v>
+      <c r="B36" s="2">
+        <v>0</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37" s="1">
         <v>33</v>
       </c>
-      <c r="B37" s="1">
-        <v>0</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>10</v>
+      <c r="B37" s="2">
+        <v>0</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38" s="1">
         <v>34</v>
       </c>
-      <c r="B38" s="1">
-        <v>0</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>10</v>
+      <c r="B38" s="2">
+        <v>0</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A39" s="1">
         <v>35</v>
       </c>
-      <c r="B39" s="1">
-        <v>0</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>10</v>
+      <c r="B39" s="2">
+        <v>0</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A40" s="1">
         <v>36</v>
       </c>
-      <c r="B40" s="1">
-        <v>0</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>10</v>
+      <c r="B40" s="2">
+        <v>0</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A41" s="1">
         <v>37</v>
       </c>
-      <c r="B41" s="1">
-        <v>0</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>10</v>
+      <c r="B41" s="2">
+        <v>0</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A42" s="1">
         <v>38</v>
       </c>
-      <c r="B42" s="1">
-        <v>0</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>10</v>
+      <c r="B42" s="2">
+        <v>0</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A43" s="1">
         <v>39</v>
       </c>
-      <c r="B43" s="1">
-        <v>0</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>10</v>
+      <c r="B43" s="2">
+        <v>0</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A44" s="1">
         <v>40</v>
       </c>
-      <c r="B44" s="1">
-        <v>0</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>10</v>
+      <c r="B44" s="2">
+        <v>0</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A45" s="1">
         <v>41</v>
       </c>
-      <c r="B45" s="1">
-        <v>0</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>10</v>
+      <c r="B45" s="2">
+        <v>0</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="1">
         <v>42</v>
       </c>
-      <c r="B46" s="1">
-        <v>0</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>10</v>
+      <c r="B46" s="2">
+        <v>0</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A47" s="1">
         <v>43</v>
       </c>
-      <c r="B47" s="1">
-        <v>0</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>10</v>
+      <c r="B47" s="2">
+        <v>0</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A48" s="1">
         <v>44</v>
       </c>
-      <c r="B48" s="1">
-        <v>0</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>10</v>
+      <c r="B48" s="2">
+        <v>0</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A49" s="1">
         <v>45</v>
       </c>
-      <c r="B49" s="1">
-        <v>0</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>10</v>
+      <c r="B49" s="2">
+        <v>0</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A50" s="1">
         <v>46</v>
       </c>
-      <c r="B50" s="1">
-        <v>0</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>10</v>
+      <c r="B50" s="2">
+        <v>0</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A51" s="1">
         <v>47</v>
       </c>
-      <c r="B51" s="1">
-        <v>0</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>10</v>
+      <c r="B51" s="2">
+        <v>0</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A52" s="1">
         <v>48</v>
       </c>
-      <c r="B52" s="1">
-        <v>0</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>10</v>
+      <c r="B52" s="2">
+        <v>0</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A53" s="1">
         <v>49</v>
       </c>
-      <c r="B53" s="1">
-        <v>0</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>10</v>
+      <c r="B53" s="2">
+        <v>0</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A54" s="1">
         <v>50</v>
       </c>
-      <c r="B54" s="1">
-        <v>0</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>10</v>
+      <c r="B54" s="2">
+        <v>0</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A55" s="1">
         <v>51</v>
       </c>
-      <c r="B55" s="1">
-        <v>0</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>10</v>
+      <c r="B55" s="2">
+        <v>0</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A56" s="1">
         <v>52</v>
       </c>
-      <c r="B56" s="1">
-        <v>0</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>10</v>
+      <c r="B56" s="2">
+        <v>0</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="1">
         <v>53</v>
       </c>
-      <c r="B57" s="1">
-        <v>0</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>10</v>
+      <c r="B57" s="2">
+        <v>0</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A58" s="1">
         <v>54</v>
       </c>
-      <c r="B58" s="1">
-        <v>0</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>10</v>
+      <c r="B58" s="2">
+        <v>0</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A59" s="1">
         <v>55</v>
       </c>
-      <c r="B59" s="1">
-        <v>0</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>10</v>
+      <c r="B59" s="2">
+        <v>0</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A60" s="1">
         <v>56</v>
       </c>
-      <c r="B60" s="1">
-        <v>0</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>10</v>
+      <c r="B60" s="2">
+        <v>0</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A61" s="1">
         <v>57</v>
       </c>
-      <c r="B61" s="1">
-        <v>0</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>10</v>
+      <c r="B61" s="2">
+        <v>0</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A62" s="1">
         <v>58</v>
       </c>
-      <c r="B62" s="1">
-        <v>0</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>10</v>
+      <c r="B62" s="2">
+        <v>0</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A63" s="1">
         <v>59</v>
       </c>
-      <c r="B63" s="1">
-        <v>0</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>10</v>
+      <c r="B63" s="2">
+        <v>0</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A64" s="1">
         <v>60</v>
       </c>
-      <c r="B64" s="1">
-        <v>0</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>10</v>
+      <c r="B64" s="2">
+        <v>0</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A65" s="1">
         <v>61</v>
       </c>
-      <c r="B65" s="1">
-        <v>0</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>10</v>
+      <c r="B65" s="2">
+        <v>0</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A66" s="1">
         <v>62</v>
       </c>
-      <c r="B66" s="1">
-        <v>0</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>10</v>
+      <c r="B66" s="2">
+        <v>0</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A67" s="1">
         <v>63</v>
       </c>
-      <c r="B67" s="1">
-        <v>0</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>10</v>
+      <c r="B67" s="2">
+        <v>0</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="1">
         <v>64</v>
       </c>
-      <c r="B68" s="1">
-        <v>0</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>10</v>
+      <c r="B68" s="2">
+        <v>0</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A69" s="1">
         <v>65</v>
       </c>
-      <c r="B69" s="1">
-        <v>0</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>10</v>
+      <c r="B69" s="2">
+        <v>0</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A70" s="1">
         <v>66</v>
       </c>
-      <c r="B70" s="1">
-        <v>0</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>10</v>
+      <c r="B70" s="2">
+        <v>0</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A71" s="1">
         <v>67</v>
       </c>
-      <c r="B71" s="1">
-        <v>0</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>10</v>
+      <c r="B71" s="2">
+        <v>0</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A72" s="1">
         <v>68</v>
       </c>
-      <c r="B72" s="1">
-        <v>0</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>10</v>
+      <c r="B72" s="2">
+        <v>0</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A73" s="1">
         <v>69</v>
       </c>
-      <c r="B73" s="1">
-        <v>0</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>10</v>
+      <c r="B73" s="2">
+        <v>0</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A74" s="1">
         <v>70</v>
       </c>
-      <c r="B74" s="1">
-        <v>0</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>10</v>
+      <c r="B74" s="2">
+        <v>0</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A75" s="1">
         <v>71</v>
       </c>
-      <c r="B75" s="1">
-        <v>0</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>10</v>
+      <c r="B75" s="2">
+        <v>0</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A76" s="1">
         <v>72</v>
       </c>
-      <c r="B76" s="1">
-        <v>0</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>10</v>
+      <c r="B76" s="2">
+        <v>0</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A77" s="1">
         <v>73</v>
       </c>
-      <c r="B77" s="1">
-        <v>0</v>
-      </c>
-      <c r="C77" s="2" t="s">
-        <v>10</v>
+      <c r="B77" s="2">
+        <v>0</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A78" s="1">
         <v>74</v>
       </c>
-      <c r="B78" s="1">
-        <v>0</v>
-      </c>
-      <c r="C78" s="2" t="s">
-        <v>10</v>
+      <c r="B78" s="2">
+        <v>0</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="1">
         <v>75</v>
       </c>
-      <c r="B79" s="1">
-        <v>0</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>10</v>
+      <c r="B79" s="2">
+        <v>0</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A80" s="1">
         <v>76</v>
       </c>
-      <c r="B80" s="1">
-        <v>0</v>
-      </c>
-      <c r="C80" s="2" t="s">
-        <v>10</v>
+      <c r="B80" s="2">
+        <v>0</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A81" s="1">
         <v>77</v>
       </c>
-      <c r="B81" s="1">
-        <v>0</v>
-      </c>
-      <c r="C81" s="2" t="s">
-        <v>10</v>
+      <c r="B81" s="2">
+        <v>0</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A82" s="1">
         <v>78</v>
       </c>
-      <c r="B82" s="1">
-        <v>0</v>
-      </c>
-      <c r="C82" s="2" t="s">
-        <v>10</v>
+      <c r="B82" s="2">
+        <v>0</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A83" s="1">
         <v>79</v>
       </c>
-      <c r="B83" s="1">
-        <v>0</v>
-      </c>
-      <c r="C83" s="2" t="s">
-        <v>10</v>
+      <c r="B83" s="2">
+        <v>0</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A84" s="1">
         <v>80</v>
       </c>
-      <c r="B84" s="1">
-        <v>0</v>
-      </c>
-      <c r="C84" s="2" t="s">
-        <v>10</v>
+      <c r="B84" s="2">
+        <v>0</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A85" s="1">
         <v>81</v>
       </c>
-      <c r="B85" s="1">
-        <v>0</v>
-      </c>
-      <c r="C85" s="2" t="s">
-        <v>10</v>
+      <c r="B85" s="2">
+        <v>0</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A86" s="1">
         <v>82</v>
       </c>
-      <c r="B86" s="1">
-        <v>0</v>
-      </c>
-      <c r="C86" s="2" t="s">
-        <v>10</v>
+      <c r="B86" s="2">
+        <v>0</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A87" s="1">
         <v>83</v>
       </c>
-      <c r="B87" s="1">
-        <v>0</v>
-      </c>
-      <c r="C87" s="2" t="s">
-        <v>10</v>
+      <c r="B87" s="2">
+        <v>0</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A88" s="1">
         <v>84</v>
       </c>
-      <c r="B88" s="1">
-        <v>0</v>
-      </c>
-      <c r="C88" s="2" t="s">
-        <v>10</v>
+      <c r="B88" s="2">
+        <v>0</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A89" s="1">
         <v>85</v>
       </c>
-      <c r="B89" s="1">
-        <v>0</v>
-      </c>
-      <c r="C89" s="2" t="s">
-        <v>10</v>
+      <c r="B89" s="2">
+        <v>0</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="1">
         <v>86</v>
       </c>
-      <c r="B90" s="1">
-        <v>0</v>
-      </c>
-      <c r="C90" s="2" t="s">
-        <v>10</v>
+      <c r="B90" s="2">
+        <v>0</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A91" s="1">
         <v>87</v>
       </c>
-      <c r="B91" s="1">
-        <v>0</v>
-      </c>
-      <c r="C91" s="2" t="s">
-        <v>10</v>
+      <c r="B91" s="2">
+        <v>0</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A92" s="1">
         <v>88</v>
       </c>
-      <c r="B92" s="1">
-        <v>0</v>
-      </c>
-      <c r="C92" s="2" t="s">
-        <v>10</v>
+      <c r="B92" s="2">
+        <v>0</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A93" s="1">
         <v>89</v>
       </c>
-      <c r="B93" s="1">
-        <v>0</v>
-      </c>
-      <c r="C93" s="2" t="s">
-        <v>10</v>
+      <c r="B93" s="2">
+        <v>0</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A94" s="1">
         <v>90</v>
       </c>
-      <c r="B94" s="1">
-        <v>0</v>
-      </c>
-      <c r="C94" s="2" t="s">
-        <v>10</v>
+      <c r="B94" s="2">
+        <v>0</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A95" s="1">
         <v>91</v>
       </c>
-      <c r="B95" s="1">
-        <v>0</v>
-      </c>
-      <c r="C95" s="2" t="s">
-        <v>10</v>
+      <c r="B95" s="2">
+        <v>0</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A96" s="1">
         <v>92</v>
       </c>
-      <c r="B96" s="1">
-        <v>0</v>
-      </c>
-      <c r="C96" s="2" t="s">
-        <v>10</v>
+      <c r="B96" s="2">
+        <v>0</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A97" s="1">
         <v>93</v>
       </c>
-      <c r="B97" s="1">
-        <v>0</v>
-      </c>
-      <c r="C97" s="2" t="s">
-        <v>10</v>
+      <c r="B97" s="2">
+        <v>0</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A98" s="1">
         <v>94</v>
       </c>
-      <c r="B98" s="1">
-        <v>0</v>
-      </c>
-      <c r="C98" s="2" t="s">
-        <v>10</v>
+      <c r="B98" s="2">
+        <v>0</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A99" s="1">
         <v>95</v>
       </c>
-      <c r="B99" s="1">
-        <v>0</v>
-      </c>
-      <c r="C99" s="2" t="s">
-        <v>10</v>
+      <c r="B99" s="2">
+        <v>0</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A100" s="1">
         <v>96</v>
       </c>
-      <c r="B100" s="1">
-        <v>0</v>
-      </c>
-      <c r="C100" s="2" t="s">
-        <v>10</v>
+      <c r="B100" s="2">
+        <v>0</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="1">
         <v>97</v>
       </c>
-      <c r="B101" s="1">
-        <v>0</v>
-      </c>
-      <c r="C101" s="2" t="s">
-        <v>10</v>
+      <c r="B101" s="2">
+        <v>0</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A102" s="1">
         <v>98</v>
       </c>
-      <c r="B102" s="1">
-        <v>0</v>
-      </c>
-      <c r="C102" s="2" t="s">
-        <v>10</v>
+      <c r="B102" s="2">
+        <v>0</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A103" s="1">
         <v>99</v>
       </c>
-      <c r="B103" s="1">
-        <v>0</v>
-      </c>
-      <c r="C103" s="2" t="s">
-        <v>10</v>
+      <c r="B103" s="2">
+        <v>0</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A104" s="1">
         <v>100</v>
       </c>
-      <c r="B104" s="1">
-        <v>0</v>
-      </c>
-      <c r="C104" s="2" t="s">
-        <v>10</v>
+      <c r="B104" s="2">
+        <v>0</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A105" s="1">
         <v>101</v>
       </c>
-      <c r="B105" s="1">
-        <v>0</v>
-      </c>
-      <c r="C105" s="2" t="s">
-        <v>10</v>
+      <c r="B105" s="2">
+        <v>0</v>
+      </c>
+      <c r="C105" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A106" s="1">
         <v>102</v>
       </c>
-      <c r="B106" s="1">
-        <v>0</v>
-      </c>
-      <c r="C106" s="2" t="s">
-        <v>10</v>
+      <c r="B106" s="2">
+        <v>0</v>
+      </c>
+      <c r="C106" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A107" s="1">
         <v>103</v>
       </c>
-      <c r="B107" s="1">
-        <v>0</v>
-      </c>
-      <c r="C107" s="2" t="s">
-        <v>10</v>
+      <c r="B107" s="2">
+        <v>0</v>
+      </c>
+      <c r="C107" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A108" s="1">
         <v>104</v>
       </c>
-      <c r="B108" s="1">
-        <v>0</v>
-      </c>
-      <c r="C108" s="2" t="s">
-        <v>10</v>
+      <c r="B108" s="2">
+        <v>0</v>
+      </c>
+      <c r="C108" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A109" s="1">
         <v>105</v>
       </c>
-      <c r="B109" s="1">
-        <v>0</v>
-      </c>
-      <c r="C109" s="2" t="s">
-        <v>10</v>
+      <c r="B109" s="2">
+        <v>0</v>
+      </c>
+      <c r="C109" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A110" s="1">
         <v>106</v>
       </c>
-      <c r="B110" s="1">
-        <v>0</v>
-      </c>
-      <c r="C110" s="2" t="s">
-        <v>10</v>
+      <c r="B110" s="2">
+        <v>0</v>
+      </c>
+      <c r="C110" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A111" s="1">
         <v>107</v>
       </c>
-      <c r="B111" s="1">
-        <v>0</v>
-      </c>
-      <c r="C111" s="2" t="s">
-        <v>10</v>
+      <c r="B111" s="2">
+        <v>0</v>
+      </c>
+      <c r="C111" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="1">
         <v>108</v>
       </c>
-      <c r="B112" s="1">
-        <v>0</v>
-      </c>
-      <c r="C112" s="2" t="s">
-        <v>10</v>
+      <c r="B112" s="2">
+        <v>0</v>
+      </c>
+      <c r="C112" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A113" s="1">
         <v>109</v>
       </c>
-      <c r="B113" s="1">
-        <v>0</v>
-      </c>
-      <c r="C113" s="2" t="s">
-        <v>10</v>
+      <c r="B113" s="2">
+        <v>0</v>
+      </c>
+      <c r="C113" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A114" s="1">
         <v>110</v>
       </c>
-      <c r="B114" s="1">
-        <v>0</v>
-      </c>
-      <c r="C114" s="2" t="s">
-        <v>10</v>
+      <c r="B114" s="2">
+        <v>0</v>
+      </c>
+      <c r="C114" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A115" s="1">
         <v>111</v>
       </c>
-      <c r="B115" s="1">
-        <v>0</v>
-      </c>
-      <c r="C115" s="2" t="s">
-        <v>10</v>
+      <c r="B115" s="2">
+        <v>0</v>
+      </c>
+      <c r="C115" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A116" s="1">
         <v>112</v>
       </c>
-      <c r="B116" s="1">
-        <v>0</v>
-      </c>
-      <c r="C116" s="2" t="s">
-        <v>10</v>
+      <c r="B116" s="2">
+        <v>0</v>
+      </c>
+      <c r="C116" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A117" s="1">
         <v>113</v>
       </c>
-      <c r="B117" s="1">
-        <v>0</v>
-      </c>
-      <c r="C117" s="2" t="s">
-        <v>10</v>
+      <c r="B117" s="2">
+        <v>0</v>
+      </c>
+      <c r="C117" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A118" s="1">
         <v>114</v>
       </c>
-      <c r="B118" s="1">
-        <v>0</v>
-      </c>
-      <c r="C118" s="2" t="s">
-        <v>10</v>
+      <c r="B118" s="2">
+        <v>0</v>
+      </c>
+      <c r="C118" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A119" s="1">
         <v>115</v>
       </c>
-      <c r="B119" s="1">
-        <v>0</v>
-      </c>
-      <c r="C119" s="2" t="s">
-        <v>10</v>
+      <c r="B119" s="2">
+        <v>0</v>
+      </c>
+      <c r="C119" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A120" s="1">
         <v>116</v>
       </c>
-      <c r="B120" s="1">
-        <v>0</v>
-      </c>
-      <c r="C120" s="2" t="s">
-        <v>10</v>
+      <c r="B120" s="2">
+        <v>0</v>
+      </c>
+      <c r="C120" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A121" s="1">
         <v>117</v>
       </c>
-      <c r="B121" s="1">
-        <v>0</v>
-      </c>
-      <c r="C121" s="2" t="s">
-        <v>10</v>
+      <c r="B121" s="2">
+        <v>0</v>
+      </c>
+      <c r="C121" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A122" s="1">
         <v>118</v>
       </c>
-      <c r="B122" s="1">
-        <v>0</v>
-      </c>
-      <c r="C122" s="2" t="s">
-        <v>10</v>
+      <c r="B122" s="2">
+        <v>0</v>
+      </c>
+      <c r="C122" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="1">
         <v>119</v>
       </c>
-      <c r="B123" s="1">
-        <v>0</v>
-      </c>
-      <c r="C123" s="2" t="s">
-        <v>10</v>
+      <c r="B123" s="2">
+        <v>0</v>
+      </c>
+      <c r="C123" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A124" s="1">
         <v>120</v>
       </c>
-      <c r="B124" s="1">
-        <v>0</v>
-      </c>
-      <c r="C124" s="2" t="s">
-        <v>10</v>
+      <c r="B124" s="2">
+        <v>0</v>
+      </c>
+      <c r="C124" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A125" s="1">
         <v>121</v>
       </c>
-      <c r="B125" s="1">
-        <v>0</v>
-      </c>
-      <c r="C125" s="2" t="s">
-        <v>10</v>
+      <c r="B125" s="2">
+        <v>0</v>
+      </c>
+      <c r="C125" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A126" s="1">
         <v>122</v>
       </c>
-      <c r="B126" s="1">
-        <v>0</v>
-      </c>
-      <c r="C126" s="2" t="s">
-        <v>10</v>
+      <c r="B126" s="2">
+        <v>0</v>
+      </c>
+      <c r="C126" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A127" s="1">
         <v>123</v>
       </c>
-      <c r="B127" s="1">
-        <v>0</v>
-      </c>
-      <c r="C127" s="2" t="s">
-        <v>10</v>
+      <c r="B127" s="2">
+        <v>0</v>
+      </c>
+      <c r="C127" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A128" s="1">
         <v>124</v>
       </c>
-      <c r="B128" s="1">
-        <v>0</v>
-      </c>
-      <c r="C128" s="2" t="s">
-        <v>10</v>
+      <c r="B128" s="2">
+        <v>0</v>
+      </c>
+      <c r="C128" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A129" s="1">
         <v>125</v>
       </c>
-      <c r="B129" s="1">
-        <v>0</v>
-      </c>
-      <c r="C129" s="2" t="s">
-        <v>10</v>
+      <c r="B129" s="2">
+        <v>0</v>
+      </c>
+      <c r="C129" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A130" s="1">
         <v>126</v>
       </c>
-      <c r="B130" s="1">
-        <v>0</v>
-      </c>
-      <c r="C130" s="2" t="s">
-        <v>10</v>
+      <c r="B130" s="2">
+        <v>0</v>
+      </c>
+      <c r="C130" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A131" s="1">
         <v>127</v>
       </c>
-      <c r="B131" s="1">
-        <v>0</v>
-      </c>
-      <c r="C131" s="2" t="s">
-        <v>10</v>
+      <c r="B131" s="2">
+        <v>0</v>
+      </c>
+      <c r="C131" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A132" s="1">
         <v>128</v>
       </c>
-      <c r="B132" s="1">
-        <v>0</v>
-      </c>
-      <c r="C132" s="2" t="s">
-        <v>10</v>
+      <c r="B132" s="2">
+        <v>0</v>
+      </c>
+      <c r="C132" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A133" s="1">
         <v>129</v>
       </c>
-      <c r="B133" s="1">
-        <v>0</v>
-      </c>
-      <c r="C133" s="2" t="s">
-        <v>10</v>
+      <c r="B133" s="2">
+        <v>0</v>
+      </c>
+      <c r="C133" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="1">
         <v>130</v>
       </c>
-      <c r="B134" s="1">
-        <v>0</v>
-      </c>
-      <c r="C134" s="2" t="s">
-        <v>10</v>
+      <c r="B134" s="2">
+        <v>0</v>
+      </c>
+      <c r="C134" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A135" s="1">
         <v>131</v>
       </c>
-      <c r="B135" s="1">
-        <v>0</v>
-      </c>
-      <c r="C135" s="2" t="s">
-        <v>10</v>
+      <c r="B135" s="2">
+        <v>0</v>
+      </c>
+      <c r="C135" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A136" s="1">
         <v>132</v>
       </c>
-      <c r="B136" s="1">
-        <v>0</v>
-      </c>
-      <c r="C136" s="2" t="s">
-        <v>10</v>
+      <c r="B136" s="2">
+        <v>0</v>
+      </c>
+      <c r="C136" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A137" s="1">
         <v>133</v>
       </c>
-      <c r="B137" s="1">
-        <v>0</v>
-      </c>
-      <c r="C137" s="2" t="s">
-        <v>10</v>
+      <c r="B137" s="2">
+        <v>0</v>
+      </c>
+      <c r="C137" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A138" s="1">
         <v>134</v>
       </c>
-      <c r="B138" s="1">
-        <v>0</v>
-      </c>
-      <c r="C138" s="2" t="s">
-        <v>10</v>
+      <c r="B138" s="2">
+        <v>0</v>
+      </c>
+      <c r="C138" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A139" s="1">
         <v>135</v>
       </c>
-      <c r="B139" s="1">
-        <v>0</v>
-      </c>
-      <c r="C139" s="2" t="s">
-        <v>10</v>
+      <c r="B139" s="2">
+        <v>0</v>
+      </c>
+      <c r="C139" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A140" s="1">
         <v>136</v>
       </c>
-      <c r="B140" s="1">
-        <v>0</v>
-      </c>
-      <c r="C140" s="2" t="s">
-        <v>10</v>
+      <c r="B140" s="2">
+        <v>0</v>
+      </c>
+      <c r="C140" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A141" s="1">
         <v>137</v>
       </c>
-      <c r="B141" s="1">
-        <v>0</v>
-      </c>
-      <c r="C141" s="2" t="s">
-        <v>10</v>
+      <c r="B141" s="2">
+        <v>0</v>
+      </c>
+      <c r="C141" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A142" s="1">
         <v>138</v>
       </c>
-      <c r="B142" s="1">
-        <v>0</v>
-      </c>
-      <c r="C142" s="2" t="s">
-        <v>10</v>
+      <c r="B142" s="2">
+        <v>0</v>
+      </c>
+      <c r="C142" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A143" s="1">
         <v>139</v>
       </c>
-      <c r="B143" s="1">
-        <v>0</v>
-      </c>
-      <c r="C143" s="2" t="s">
-        <v>10</v>
+      <c r="B143" s="2">
+        <v>0</v>
+      </c>
+      <c r="C143" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A144" s="1">
         <v>140</v>
       </c>
-      <c r="B144" s="1">
-        <v>0</v>
-      </c>
-      <c r="C144" s="2" t="s">
-        <v>10</v>
+      <c r="B144" s="2">
+        <v>0</v>
+      </c>
+      <c r="C144" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="1">
         <v>141</v>
       </c>
-      <c r="B145" s="1">
-        <v>0</v>
-      </c>
-      <c r="C145" s="2" t="s">
-        <v>10</v>
+      <c r="B145" s="2">
+        <v>0</v>
+      </c>
+      <c r="C145" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A146" s="1">
         <v>142</v>
       </c>
-      <c r="B146" s="1">
-        <v>0</v>
-      </c>
-      <c r="C146" s="2" t="s">
-        <v>10</v>
+      <c r="B146" s="2">
+        <v>0</v>
+      </c>
+      <c r="C146" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A147" s="1">
         <v>143</v>
       </c>
-      <c r="B147" s="1">
-        <v>0</v>
-      </c>
-      <c r="C147" s="2" t="s">
-        <v>10</v>
+      <c r="B147" s="2">
+        <v>0</v>
+      </c>
+      <c r="C147" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A148" s="1">
         <v>144</v>
       </c>
-      <c r="B148" s="1">
-        <v>0</v>
-      </c>
-      <c r="C148" s="2" t="s">
-        <v>10</v>
+      <c r="B148" s="2">
+        <v>0</v>
+      </c>
+      <c r="C148" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A149" s="1">
         <v>145</v>
       </c>
-      <c r="B149" s="1">
-        <v>0</v>
-      </c>
-      <c r="C149" s="2" t="s">
-        <v>10</v>
+      <c r="B149" s="2">
+        <v>0</v>
+      </c>
+      <c r="C149" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A150" s="1">
         <v>146</v>
       </c>
-      <c r="B150" s="1">
-        <v>0</v>
-      </c>
-      <c r="C150" s="2" t="s">
-        <v>10</v>
+      <c r="B150" s="2">
+        <v>0</v>
+      </c>
+      <c r="C150" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A151" s="1">
         <v>147</v>
       </c>
-      <c r="B151" s="1">
-        <v>0</v>
-      </c>
-      <c r="C151" s="2" t="s">
-        <v>10</v>
+      <c r="B151" s="2">
+        <v>0</v>
+      </c>
+      <c r="C151" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A152" s="1">
         <v>148</v>
       </c>
-      <c r="B152" s="1">
-        <v>0</v>
-      </c>
-      <c r="C152" s="2" t="s">
-        <v>10</v>
+      <c r="B152" s="2">
+        <v>0</v>
+      </c>
+      <c r="C152" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A153" s="1">
         <v>149</v>
       </c>
-      <c r="B153" s="1">
-        <v>0</v>
-      </c>
-      <c r="C153" s="2" t="s">
-        <v>10</v>
+      <c r="B153" s="2">
+        <v>0</v>
+      </c>
+      <c r="C153" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A154" s="1">
         <v>150</v>
       </c>
-      <c r="B154" s="1">
-        <v>0</v>
-      </c>
-      <c r="C154" s="2" t="s">
-        <v>10</v>
+      <c r="B154" s="2">
+        <v>0</v>
+      </c>
+      <c r="C154" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A155" s="1">
         <v>151</v>
       </c>
-      <c r="B155" s="1">
-        <v>0</v>
-      </c>
-      <c r="C155" s="2" t="s">
-        <v>10</v>
+      <c r="B155" s="2">
+        <v>0</v>
+      </c>
+      <c r="C155" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="1">
         <v>152</v>
       </c>
-      <c r="B156" s="1">
-        <v>0</v>
-      </c>
-      <c r="C156" s="2" t="s">
-        <v>10</v>
+      <c r="B156" s="2">
+        <v>0</v>
+      </c>
+      <c r="C156" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A157" s="1">
         <v>153</v>
       </c>
-      <c r="B157" s="1">
-        <v>0</v>
-      </c>
-      <c r="C157" s="2" t="s">
-        <v>10</v>
+      <c r="B157" s="2">
+        <v>0</v>
+      </c>
+      <c r="C157" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A158" s="1">
         <v>154</v>
       </c>
-      <c r="B158" s="1">
-        <v>0</v>
-      </c>
-      <c r="C158" s="2" t="s">
-        <v>10</v>
+      <c r="B158" s="2">
+        <v>0</v>
+      </c>
+      <c r="C158" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A159" s="1">
         <v>155</v>
       </c>
-      <c r="B159" s="1">
-        <v>0</v>
-      </c>
-      <c r="C159" s="2" t="s">
-        <v>10</v>
+      <c r="B159" s="2">
+        <v>0</v>
+      </c>
+      <c r="C159" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A160" s="1">
         <v>156</v>
       </c>
-      <c r="B160" s="1">
-        <v>0</v>
-      </c>
-      <c r="C160" s="2" t="s">
-        <v>10</v>
+      <c r="B160" s="2">
+        <v>0</v>
+      </c>
+      <c r="C160" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A161" s="1">
         <v>157</v>
       </c>
-      <c r="B161" s="1">
-        <v>0</v>
-      </c>
-      <c r="C161" s="2" t="s">
-        <v>10</v>
+      <c r="B161" s="2">
+        <v>0</v>
+      </c>
+      <c r="C161" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A162" s="1">
         <v>158</v>
       </c>
-      <c r="B162" s="1">
-        <v>0</v>
-      </c>
-      <c r="C162" s="2" t="s">
-        <v>10</v>
+      <c r="B162" s="2">
+        <v>0</v>
+      </c>
+      <c r="C162" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A163" s="1">
         <v>159</v>
       </c>
-      <c r="B163" s="1">
-        <v>0</v>
-      </c>
-      <c r="C163" s="2" t="s">
-        <v>10</v>
+      <c r="B163" s="2">
+        <v>0</v>
+      </c>
+      <c r="C163" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A164" s="1">
         <v>160</v>
       </c>
-      <c r="B164" s="1">
-        <v>0</v>
-      </c>
-      <c r="C164" s="2" t="s">
-        <v>10</v>
+      <c r="B164" s="2">
+        <v>0</v>
+      </c>
+      <c r="C164" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/servers/maze_main_server/conf.d/data/maze_equ_drop_v8【迷宫-装备掉落概率】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_equ_drop_v8【迷宫-装备掉落概率】.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95505669-BBBF-46E9-9D12-6767AB1C35BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{623440C4-66A2-40FD-AC34-1C95BADB4217}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="28">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -116,6 +116,18 @@
   </si>
   <si>
     <t>0:0</t>
+  </si>
+  <si>
+    <t>3,5,1,3</t>
+  </si>
+  <si>
+    <t>1,7,3,4</t>
+  </si>
+  <si>
+    <t>3,6,5,1</t>
+  </si>
+  <si>
+    <t>5,8,3,7</t>
   </si>
 </sst>
 </file>
@@ -539,8 +551,8 @@
       <c r="A8" s="1">
         <v>4</v>
       </c>
-      <c r="B8" s="2">
-        <v>0</v>
+      <c r="B8" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>16</v>
@@ -550,8 +562,8 @@
       <c r="A9" s="1">
         <v>5</v>
       </c>
-      <c r="B9" s="2">
-        <v>0</v>
+      <c r="B9" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>17</v>
@@ -561,8 +573,8 @@
       <c r="A10" s="1">
         <v>6</v>
       </c>
-      <c r="B10" s="2">
-        <v>0</v>
+      <c r="B10" s="2" t="s">
+        <v>26</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>18</v>
@@ -572,8 +584,8 @@
       <c r="A11" s="1">
         <v>7</v>
       </c>
-      <c r="B11" s="2">
-        <v>0</v>
+      <c r="B11" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>19</v>

--- a/servers/maze_main_server/conf.d/data/maze_equ_drop_v8【迷宫-装备掉落概率】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_equ_drop_v8【迷宫-装备掉落概率】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{623440C4-66A2-40FD-AC34-1C95BADB4217}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0360E517-16AB-475D-9CF6-1BBF19207B4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -76,21 +76,12 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1,8,3,3,1,5</t>
-  </si>
-  <si>
     <t>1:8000_3:2000_5:0_6:0</t>
   </si>
   <si>
-    <t>1,7,3,2,1,4</t>
-  </si>
-  <si>
     <t>1:7000_3:3000_5:0_6:0</t>
   </si>
   <si>
-    <t>3,1,1,6,3,8</t>
-  </si>
-  <si>
     <t>1:6000_3:4000_5:0_6:0</t>
   </si>
   <si>
@@ -121,13 +112,22 @@
     <t>3,5,1,3</t>
   </si>
   <si>
-    <t>1,7,3,4</t>
-  </si>
-  <si>
     <t>3,6,5,1</t>
   </si>
   <si>
     <t>5,8,3,7</t>
+  </si>
+  <si>
+    <t>1,7,3,3,1,5</t>
+  </si>
+  <si>
+    <t>1,8,3,2,1,4</t>
+  </si>
+  <si>
+    <t>3,1,1,6,3,7</t>
+  </si>
+  <si>
+    <t>1,8,3,4</t>
   </si>
 </sst>
 </file>
@@ -519,10 +519,10 @@
         <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>10</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -530,10 +530,10 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
@@ -541,10 +541,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -552,10 +552,10 @@
         <v>4</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
@@ -563,10 +563,10 @@
         <v>5</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -574,10 +574,10 @@
         <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
@@ -585,10 +585,10 @@
         <v>7</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
@@ -599,7 +599,7 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
@@ -621,7 +621,7 @@
         <v>0</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -632,7 +632,7 @@
         <v>0</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
@@ -643,7 +643,7 @@
         <v>0</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
@@ -654,7 +654,7 @@
         <v>0</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
@@ -665,7 +665,7 @@
         <v>0</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
@@ -676,7 +676,7 @@
         <v>0</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -687,7 +687,7 @@
         <v>0</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -698,7 +698,7 @@
         <v>0</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -709,7 +709,7 @@
         <v>0</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -720,7 +720,7 @@
         <v>0</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -731,7 +731,7 @@
         <v>0</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -742,7 +742,7 @@
         <v>0</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
@@ -753,7 +753,7 @@
         <v>0</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
@@ -764,7 +764,7 @@
         <v>0</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
@@ -775,7 +775,7 @@
         <v>0</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -786,7 +786,7 @@
         <v>0</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -797,7 +797,7 @@
         <v>0</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
@@ -808,7 +808,7 @@
         <v>0</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
@@ -819,7 +819,7 @@
         <v>0</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -830,7 +830,7 @@
         <v>0</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
@@ -841,7 +841,7 @@
         <v>0</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -852,7 +852,7 @@
         <v>0</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
@@ -863,7 +863,7 @@
         <v>0</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
@@ -874,7 +874,7 @@
         <v>0</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
@@ -885,7 +885,7 @@
         <v>0</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.2">
@@ -896,7 +896,7 @@
         <v>0</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.2">
@@ -907,7 +907,7 @@
         <v>0</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.2">
@@ -918,7 +918,7 @@
         <v>0</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.2">
@@ -929,7 +929,7 @@
         <v>0</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.2">
@@ -940,7 +940,7 @@
         <v>0</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
@@ -951,7 +951,7 @@
         <v>0</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.2">
@@ -962,7 +962,7 @@
         <v>0</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
@@ -973,7 +973,7 @@
         <v>0</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.2">
@@ -984,7 +984,7 @@
         <v>0</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.2">
@@ -995,7 +995,7 @@
         <v>0</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.2">
@@ -1006,7 +1006,7 @@
         <v>0</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.2">
@@ -1017,7 +1017,7 @@
         <v>0</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.2">
@@ -1028,7 +1028,7 @@
         <v>0</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.2">
@@ -1039,7 +1039,7 @@
         <v>0</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.2">
@@ -1050,7 +1050,7 @@
         <v>0</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.2">
@@ -1061,7 +1061,7 @@
         <v>0</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.2">
@@ -1072,7 +1072,7 @@
         <v>0</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.2">
@@ -1083,7 +1083,7 @@
         <v>0</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
@@ -1094,7 +1094,7 @@
         <v>0</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.2">
@@ -1105,7 +1105,7 @@
         <v>0</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.2">
@@ -1116,7 +1116,7 @@
         <v>0</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.2">
@@ -1127,7 +1127,7 @@
         <v>0</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.2">
@@ -1138,7 +1138,7 @@
         <v>0</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.2">
@@ -1149,7 +1149,7 @@
         <v>0</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.2">
@@ -1160,7 +1160,7 @@
         <v>0</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.2">
@@ -1171,7 +1171,7 @@
         <v>0</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.2">
@@ -1182,7 +1182,7 @@
         <v>0</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.2">
@@ -1193,7 +1193,7 @@
         <v>0</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.2">
@@ -1204,7 +1204,7 @@
         <v>0</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
@@ -1215,7 +1215,7 @@
         <v>0</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.2">
@@ -1226,7 +1226,7 @@
         <v>0</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.2">
@@ -1237,7 +1237,7 @@
         <v>0</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.2">
@@ -1248,7 +1248,7 @@
         <v>0</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.2">
@@ -1259,7 +1259,7 @@
         <v>0</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.2">
@@ -1270,7 +1270,7 @@
         <v>0</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.2">
@@ -1281,7 +1281,7 @@
         <v>0</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.2">
@@ -1292,7 +1292,7 @@
         <v>0</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.2">
@@ -1303,7 +1303,7 @@
         <v>0</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.2">
@@ -1314,7 +1314,7 @@
         <v>0</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.2">
@@ -1325,7 +1325,7 @@
         <v>0</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
@@ -1336,7 +1336,7 @@
         <v>0</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.2">
@@ -1347,7 +1347,7 @@
         <v>0</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.2">
@@ -1358,7 +1358,7 @@
         <v>0</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.2">
@@ -1369,7 +1369,7 @@
         <v>0</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.2">
@@ -1380,7 +1380,7 @@
         <v>0</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.2">
@@ -1391,7 +1391,7 @@
         <v>0</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.2">
@@ -1402,7 +1402,7 @@
         <v>0</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.2">
@@ -1413,7 +1413,7 @@
         <v>0</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.2">
@@ -1424,7 +1424,7 @@
         <v>0</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.2">
@@ -1435,7 +1435,7 @@
         <v>0</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.2">
@@ -1446,7 +1446,7 @@
         <v>0</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
@@ -1457,7 +1457,7 @@
         <v>0</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.2">
@@ -1468,7 +1468,7 @@
         <v>0</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.2">
@@ -1479,7 +1479,7 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.2">
@@ -1490,7 +1490,7 @@
         <v>0</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.2">
@@ -1501,7 +1501,7 @@
         <v>0</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.2">
@@ -1512,7 +1512,7 @@
         <v>0</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.2">
@@ -1523,7 +1523,7 @@
         <v>0</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.2">
@@ -1534,7 +1534,7 @@
         <v>0</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.2">
@@ -1545,7 +1545,7 @@
         <v>0</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.2">
@@ -1556,7 +1556,7 @@
         <v>0</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.2">
@@ -1567,7 +1567,7 @@
         <v>0</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
@@ -1578,7 +1578,7 @@
         <v>0</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.2">
@@ -1589,7 +1589,7 @@
         <v>0</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.2">
@@ -1600,7 +1600,7 @@
         <v>0</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.2">
@@ -1611,7 +1611,7 @@
         <v>0</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.2">
@@ -1622,7 +1622,7 @@
         <v>0</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.2">
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.2">
@@ -1644,7 +1644,7 @@
         <v>0</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.2">
@@ -1655,7 +1655,7 @@
         <v>0</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.2">
@@ -1666,7 +1666,7 @@
         <v>0</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.2">
@@ -1677,7 +1677,7 @@
         <v>0</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.2">
@@ -1688,7 +1688,7 @@
         <v>0</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
@@ -1699,7 +1699,7 @@
         <v>0</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.2">
@@ -1710,7 +1710,7 @@
         <v>0</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.2">
@@ -1721,7 +1721,7 @@
         <v>0</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.2">
@@ -1732,7 +1732,7 @@
         <v>0</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.2">
@@ -1743,7 +1743,7 @@
         <v>0</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.2">
@@ -1754,7 +1754,7 @@
         <v>0</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.2">
@@ -1765,7 +1765,7 @@
         <v>0</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.2">
@@ -1776,7 +1776,7 @@
         <v>0</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.2">
@@ -1787,7 +1787,7 @@
         <v>0</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.2">
@@ -1798,7 +1798,7 @@
         <v>0</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.2">
@@ -1809,7 +1809,7 @@
         <v>0</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
@@ -1820,7 +1820,7 @@
         <v>0</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.2">
@@ -1831,7 +1831,7 @@
         <v>0</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.2">
@@ -1842,7 +1842,7 @@
         <v>0</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.2">
@@ -1853,7 +1853,7 @@
         <v>0</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.2">
@@ -1864,7 +1864,7 @@
         <v>0</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.2">
@@ -1875,7 +1875,7 @@
         <v>0</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.2">
@@ -1886,7 +1886,7 @@
         <v>0</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.2">
@@ -1897,7 +1897,7 @@
         <v>0</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.2">
@@ -1908,7 +1908,7 @@
         <v>0</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.2">
@@ -1919,7 +1919,7 @@
         <v>0</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.2">
@@ -1930,7 +1930,7 @@
         <v>0</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
@@ -1941,7 +1941,7 @@
         <v>0</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.2">
@@ -1952,7 +1952,7 @@
         <v>0</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.2">
@@ -1963,7 +1963,7 @@
         <v>0</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.2">
@@ -1974,7 +1974,7 @@
         <v>0</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.2">
@@ -1985,7 +1985,7 @@
         <v>0</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.2">
@@ -1996,7 +1996,7 @@
         <v>0</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.2">
@@ -2007,7 +2007,7 @@
         <v>0</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.2">
@@ -2018,7 +2018,7 @@
         <v>0</v>
       </c>
       <c r="C141" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.2">
@@ -2029,7 +2029,7 @@
         <v>0</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.2">
@@ -2040,7 +2040,7 @@
         <v>0</v>
       </c>
       <c r="C143" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.2">
@@ -2051,7 +2051,7 @@
         <v>0</v>
       </c>
       <c r="C144" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
@@ -2062,7 +2062,7 @@
         <v>0</v>
       </c>
       <c r="C145" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.2">
@@ -2073,7 +2073,7 @@
         <v>0</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.2">
@@ -2084,7 +2084,7 @@
         <v>0</v>
       </c>
       <c r="C147" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.2">
@@ -2095,7 +2095,7 @@
         <v>0</v>
       </c>
       <c r="C148" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.2">
@@ -2106,7 +2106,7 @@
         <v>0</v>
       </c>
       <c r="C149" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.2">
@@ -2117,7 +2117,7 @@
         <v>0</v>
       </c>
       <c r="C150" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.2">
@@ -2128,7 +2128,7 @@
         <v>0</v>
       </c>
       <c r="C151" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.2">
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="C152" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.2">
@@ -2150,7 +2150,7 @@
         <v>0</v>
       </c>
       <c r="C153" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.2">
@@ -2161,7 +2161,7 @@
         <v>0</v>
       </c>
       <c r="C154" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.2">
@@ -2172,7 +2172,7 @@
         <v>0</v>
       </c>
       <c r="C155" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
@@ -2183,7 +2183,7 @@
         <v>0</v>
       </c>
       <c r="C156" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.2">
@@ -2194,7 +2194,7 @@
         <v>0</v>
       </c>
       <c r="C157" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.2">
@@ -2205,7 +2205,7 @@
         <v>0</v>
       </c>
       <c r="C158" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.2">
@@ -2216,7 +2216,7 @@
         <v>0</v>
       </c>
       <c r="C159" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.2">
@@ -2227,7 +2227,7 @@
         <v>0</v>
       </c>
       <c r="C160" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.2">
@@ -2238,7 +2238,7 @@
         <v>0</v>
       </c>
       <c r="C161" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.2">
@@ -2249,7 +2249,7 @@
         <v>0</v>
       </c>
       <c r="C162" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.2">
@@ -2260,7 +2260,7 @@
         <v>0</v>
       </c>
       <c r="C163" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.2">
@@ -2271,7 +2271,7 @@
         <v>0</v>
       </c>
       <c r="C164" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/servers/maze_main_server/conf.d/data/maze_equ_drop_v8【迷宫-装备掉落概率】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_equ_drop_v8【迷宫-装备掉落概率】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0360E517-16AB-475D-9CF6-1BBF19207B4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6D84655-B2C2-4CFA-8B72-04F43AE91830}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -88,30 +88,9 @@
     <t>1:5000_3:4500_5:500_6:0</t>
   </si>
   <si>
-    <t>1:4000_3:5000_5:1000_6:0</t>
-  </si>
-  <si>
-    <t>1:3000_3:5500_5:1500_6:0</t>
-  </si>
-  <si>
-    <t>1:1800_3:6000_5:2000_6:200</t>
-  </si>
-  <si>
-    <t>1:1600_3:6000_5:2200_6:200</t>
-  </si>
-  <si>
-    <t>1:1400_3:6000_5:2400_6:200</t>
-  </si>
-  <si>
-    <t>1:1200_3:6000_5:2600_6:200</t>
-  </si>
-  <si>
     <t>0:0</t>
   </si>
   <si>
-    <t>3,5,1,3</t>
-  </si>
-  <si>
     <t>3,6,5,1</t>
   </si>
   <si>
@@ -124,10 +103,31 @@
     <t>1,8,3,2,1,4</t>
   </si>
   <si>
-    <t>3,1,1,6,3,7</t>
-  </si>
-  <si>
-    <t>1,8,3,4</t>
+    <t>3,1,1,6,5,7</t>
+  </si>
+  <si>
+    <t>3,5,6,3</t>
+  </si>
+  <si>
+    <t>5,8,3,4</t>
+  </si>
+  <si>
+    <t>1:3500_3:5000_5:1000_6:500</t>
+  </si>
+  <si>
+    <t>1:2500_3:5500_5:1500_6:500</t>
+  </si>
+  <si>
+    <t>1:1500_3:6000_5:2000_6:500</t>
+  </si>
+  <si>
+    <t>1:1300_3:6000_5:2200_6:500</t>
+  </si>
+  <si>
+    <t>1:1100_3:6000_5:2400_6:500</t>
+  </si>
+  <si>
+    <t>1:900_3:6000_5:2600_6:500</t>
   </si>
 </sst>
 </file>
@@ -519,7 +519,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>10</v>
@@ -530,7 +530,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>11</v>
@@ -541,7 +541,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>12</v>
@@ -552,7 +552,7 @@
         <v>4</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>13</v>
@@ -563,10 +563,10 @@
         <v>5</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -574,10 +574,10 @@
         <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
@@ -585,10 +585,10 @@
         <v>7</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
@@ -599,7 +599,7 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
@@ -621,7 +621,7 @@
         <v>0</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -632,7 +632,7 @@
         <v>0</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
@@ -643,7 +643,7 @@
         <v>0</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
@@ -654,7 +654,7 @@
         <v>0</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
@@ -665,7 +665,7 @@
         <v>0</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
@@ -676,7 +676,7 @@
         <v>0</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -687,7 +687,7 @@
         <v>0</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -698,7 +698,7 @@
         <v>0</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -709,7 +709,7 @@
         <v>0</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -720,7 +720,7 @@
         <v>0</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -731,7 +731,7 @@
         <v>0</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -742,7 +742,7 @@
         <v>0</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
@@ -753,7 +753,7 @@
         <v>0</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
@@ -764,7 +764,7 @@
         <v>0</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
@@ -775,7 +775,7 @@
         <v>0</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -786,7 +786,7 @@
         <v>0</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -797,7 +797,7 @@
         <v>0</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
@@ -808,7 +808,7 @@
         <v>0</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
@@ -819,7 +819,7 @@
         <v>0</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -830,7 +830,7 @@
         <v>0</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
@@ -841,7 +841,7 @@
         <v>0</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -852,7 +852,7 @@
         <v>0</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
@@ -863,7 +863,7 @@
         <v>0</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
@@ -874,7 +874,7 @@
         <v>0</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
@@ -885,7 +885,7 @@
         <v>0</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.2">
@@ -896,7 +896,7 @@
         <v>0</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.2">
@@ -907,7 +907,7 @@
         <v>0</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.2">
@@ -918,7 +918,7 @@
         <v>0</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.2">
@@ -929,7 +929,7 @@
         <v>0</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.2">
@@ -940,7 +940,7 @@
         <v>0</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
@@ -951,7 +951,7 @@
         <v>0</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.2">
@@ -962,7 +962,7 @@
         <v>0</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
@@ -973,7 +973,7 @@
         <v>0</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.2">
@@ -984,7 +984,7 @@
         <v>0</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.2">
@@ -995,7 +995,7 @@
         <v>0</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.2">
@@ -1006,7 +1006,7 @@
         <v>0</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.2">
@@ -1017,7 +1017,7 @@
         <v>0</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.2">
@@ -1028,7 +1028,7 @@
         <v>0</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.2">
@@ -1039,7 +1039,7 @@
         <v>0</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.2">
@@ -1050,7 +1050,7 @@
         <v>0</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.2">
@@ -1061,7 +1061,7 @@
         <v>0</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.2">
@@ -1072,7 +1072,7 @@
         <v>0</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.2">
@@ -1083,7 +1083,7 @@
         <v>0</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
@@ -1094,7 +1094,7 @@
         <v>0</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.2">
@@ -1105,7 +1105,7 @@
         <v>0</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.2">
@@ -1116,7 +1116,7 @@
         <v>0</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.2">
@@ -1127,7 +1127,7 @@
         <v>0</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.2">
@@ -1138,7 +1138,7 @@
         <v>0</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.2">
@@ -1149,7 +1149,7 @@
         <v>0</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.2">
@@ -1160,7 +1160,7 @@
         <v>0</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.2">
@@ -1171,7 +1171,7 @@
         <v>0</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.2">
@@ -1182,7 +1182,7 @@
         <v>0</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.2">
@@ -1193,7 +1193,7 @@
         <v>0</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.2">
@@ -1204,7 +1204,7 @@
         <v>0</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
@@ -1215,7 +1215,7 @@
         <v>0</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.2">
@@ -1226,7 +1226,7 @@
         <v>0</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.2">
@@ -1237,7 +1237,7 @@
         <v>0</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.2">
@@ -1248,7 +1248,7 @@
         <v>0</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.2">
@@ -1259,7 +1259,7 @@
         <v>0</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.2">
@@ -1270,7 +1270,7 @@
         <v>0</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.2">
@@ -1281,7 +1281,7 @@
         <v>0</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.2">
@@ -1292,7 +1292,7 @@
         <v>0</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.2">
@@ -1303,7 +1303,7 @@
         <v>0</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.2">
@@ -1314,7 +1314,7 @@
         <v>0</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.2">
@@ -1325,7 +1325,7 @@
         <v>0</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
@@ -1336,7 +1336,7 @@
         <v>0</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.2">
@@ -1347,7 +1347,7 @@
         <v>0</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.2">
@@ -1358,7 +1358,7 @@
         <v>0</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.2">
@@ -1369,7 +1369,7 @@
         <v>0</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.2">
@@ -1380,7 +1380,7 @@
         <v>0</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.2">
@@ -1391,7 +1391,7 @@
         <v>0</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.2">
@@ -1402,7 +1402,7 @@
         <v>0</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.2">
@@ -1413,7 +1413,7 @@
         <v>0</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.2">
@@ -1424,7 +1424,7 @@
         <v>0</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.2">
@@ -1435,7 +1435,7 @@
         <v>0</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.2">
@@ -1446,7 +1446,7 @@
         <v>0</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
@@ -1457,7 +1457,7 @@
         <v>0</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.2">
@@ -1468,7 +1468,7 @@
         <v>0</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.2">
@@ -1479,7 +1479,7 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.2">
@@ -1490,7 +1490,7 @@
         <v>0</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.2">
@@ -1501,7 +1501,7 @@
         <v>0</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.2">
@@ -1512,7 +1512,7 @@
         <v>0</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.2">
@@ -1523,7 +1523,7 @@
         <v>0</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.2">
@@ -1534,7 +1534,7 @@
         <v>0</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.2">
@@ -1545,7 +1545,7 @@
         <v>0</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.2">
@@ -1556,7 +1556,7 @@
         <v>0</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.2">
@@ -1567,7 +1567,7 @@
         <v>0</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
@@ -1578,7 +1578,7 @@
         <v>0</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.2">
@@ -1589,7 +1589,7 @@
         <v>0</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.2">
@@ -1600,7 +1600,7 @@
         <v>0</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.2">
@@ -1611,7 +1611,7 @@
         <v>0</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.2">
@@ -1622,7 +1622,7 @@
         <v>0</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.2">
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.2">
@@ -1644,7 +1644,7 @@
         <v>0</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.2">
@@ -1655,7 +1655,7 @@
         <v>0</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.2">
@@ -1666,7 +1666,7 @@
         <v>0</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.2">
@@ -1677,7 +1677,7 @@
         <v>0</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.2">
@@ -1688,7 +1688,7 @@
         <v>0</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
@@ -1699,7 +1699,7 @@
         <v>0</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.2">
@@ -1710,7 +1710,7 @@
         <v>0</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.2">
@@ -1721,7 +1721,7 @@
         <v>0</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.2">
@@ -1732,7 +1732,7 @@
         <v>0</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.2">
@@ -1743,7 +1743,7 @@
         <v>0</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.2">
@@ -1754,7 +1754,7 @@
         <v>0</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.2">
@@ -1765,7 +1765,7 @@
         <v>0</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.2">
@@ -1776,7 +1776,7 @@
         <v>0</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.2">
@@ -1787,7 +1787,7 @@
         <v>0</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.2">
@@ -1798,7 +1798,7 @@
         <v>0</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.2">
@@ -1809,7 +1809,7 @@
         <v>0</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
@@ -1820,7 +1820,7 @@
         <v>0</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.2">
@@ -1831,7 +1831,7 @@
         <v>0</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.2">
@@ -1842,7 +1842,7 @@
         <v>0</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.2">
@@ -1853,7 +1853,7 @@
         <v>0</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.2">
@@ -1864,7 +1864,7 @@
         <v>0</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.2">
@@ -1875,7 +1875,7 @@
         <v>0</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.2">
@@ -1886,7 +1886,7 @@
         <v>0</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.2">
@@ -1897,7 +1897,7 @@
         <v>0</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.2">
@@ -1908,7 +1908,7 @@
         <v>0</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.2">
@@ -1919,7 +1919,7 @@
         <v>0</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.2">
@@ -1930,7 +1930,7 @@
         <v>0</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
@@ -1941,7 +1941,7 @@
         <v>0</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.2">
@@ -1952,7 +1952,7 @@
         <v>0</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.2">
@@ -1963,7 +1963,7 @@
         <v>0</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.2">
@@ -1974,7 +1974,7 @@
         <v>0</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.2">
@@ -1985,7 +1985,7 @@
         <v>0</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.2">
@@ -1996,7 +1996,7 @@
         <v>0</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.2">
@@ -2007,7 +2007,7 @@
         <v>0</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.2">
@@ -2018,7 +2018,7 @@
         <v>0</v>
       </c>
       <c r="C141" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.2">
@@ -2029,7 +2029,7 @@
         <v>0</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.2">
@@ -2040,7 +2040,7 @@
         <v>0</v>
       </c>
       <c r="C143" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.2">
@@ -2051,7 +2051,7 @@
         <v>0</v>
       </c>
       <c r="C144" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
@@ -2062,7 +2062,7 @@
         <v>0</v>
       </c>
       <c r="C145" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.2">
@@ -2073,7 +2073,7 @@
         <v>0</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.2">
@@ -2084,7 +2084,7 @@
         <v>0</v>
       </c>
       <c r="C147" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.2">
@@ -2095,7 +2095,7 @@
         <v>0</v>
       </c>
       <c r="C148" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.2">
@@ -2106,7 +2106,7 @@
         <v>0</v>
       </c>
       <c r="C149" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.2">
@@ -2117,7 +2117,7 @@
         <v>0</v>
       </c>
       <c r="C150" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.2">
@@ -2128,7 +2128,7 @@
         <v>0</v>
       </c>
       <c r="C151" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.2">
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="C152" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.2">
@@ -2150,7 +2150,7 @@
         <v>0</v>
       </c>
       <c r="C153" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.2">
@@ -2161,7 +2161,7 @@
         <v>0</v>
       </c>
       <c r="C154" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.2">
@@ -2172,7 +2172,7 @@
         <v>0</v>
       </c>
       <c r="C155" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
@@ -2183,7 +2183,7 @@
         <v>0</v>
       </c>
       <c r="C156" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.2">
@@ -2194,7 +2194,7 @@
         <v>0</v>
       </c>
       <c r="C157" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.2">
@@ -2205,7 +2205,7 @@
         <v>0</v>
       </c>
       <c r="C158" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.2">
@@ -2216,7 +2216,7 @@
         <v>0</v>
       </c>
       <c r="C159" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.2">
@@ -2227,7 +2227,7 @@
         <v>0</v>
       </c>
       <c r="C160" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.2">
@@ -2238,7 +2238,7 @@
         <v>0</v>
       </c>
       <c r="C161" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.2">
@@ -2249,7 +2249,7 @@
         <v>0</v>
       </c>
       <c r="C162" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.2">
@@ -2260,7 +2260,7 @@
         <v>0</v>
       </c>
       <c r="C163" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.2">
@@ -2271,7 +2271,7 @@
         <v>0</v>
       </c>
       <c r="C164" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
